--- a/output/pdf_financials_xlsx/CH.xlsx
+++ b/output/pdf_financials_xlsx/CH.xlsx
@@ -1528,13 +1528,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.055123</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.452739</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.016292</v>
       </c>
     </row>
     <row r="35">
@@ -1584,13 +1584,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.055123</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.452739</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.016292</v>
       </c>
     </row>
     <row r="37">
@@ -1920,13 +1920,13 @@
         <v>0.347234</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.139006</v>
+        <v>0.083883</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.509002</v>
+        <v>0.056263</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.963821</v>
+        <v>0.947529</v>
       </c>
     </row>
     <row r="49">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/CH.xlsx
+++ b/output/pdf_financials_xlsx/CH.xlsx
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.002974</v>
+        <v>0.070314</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.007663</v>
+        <v>0.141731</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.023299</v>
+        <v>0.276685</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.023646</v>
+        <v>0.2982</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.024129</v>
+        <v>0.333842</v>
       </c>
     </row>
     <row r="29">
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.169213</v>
+        <v>-2.915827</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.814047</v>
+        <v>-2.539493</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.651987</v>
+        <v>-2.342274</v>
       </c>
     </row>
     <row r="30">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-863.8591202536892</v>
+        <v>-779.5762433500229</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-1052.204601632274</v>
+        <v>-929.3226102102435</v>
       </c>
     </row>
     <row r="31">
@@ -3413,19 +3413,19 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.070314</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.141731</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.276685</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.2982</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.333841</v>
       </c>
     </row>
     <row r="101">
@@ -8989,7 +8989,11 @@
           <t>Depreciation of property, plant and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -9085,7 +9089,11 @@
           <t>Depreciation of right-of-use-assets (Note 7)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -9183,7 +9191,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -14092,7 +14100,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -14186,7 +14198,11 @@
           <t>Depreciation of right-of-use-assets</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -14286,7 +14302,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -16740,7 +16756,11 @@
           <t>Depreciation of property, plant and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -16787,7 +16807,11 @@
           <t>Depreciation of right-of-use-assets (Note 7)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -16887,7 +16911,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -19856,7 +19880,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -19903,7 +19931,11 @@
           <t>Depreciation of right-of-use-assets</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -20003,7 +20035,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">

--- a/output/pdf_financials_xlsx/CH.xlsx
+++ b/output/pdf_financials_xlsx/CH.xlsx
@@ -1693,16 +1693,16 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.056422</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.063647</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.045697</v>
       </c>
     </row>
     <row r="41">
@@ -1721,16 +1721,16 @@
         <v>0.208965</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.261702</v>
+        <v>0.318124</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.161589</v>
+        <v>0.225236</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.115839</v>
+        <v>0.170839</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.423116</v>
+        <v>0.468813</v>
       </c>
     </row>
     <row r="42">
@@ -1917,16 +1917,16 @@
         <v>0.008836</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.347234</v>
+        <v>0.290812</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.083883</v>
+        <v>0.020236</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.056263</v>
+        <v>0.001263</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.947529</v>
+        <v>0.901832</v>
       </c>
     </row>
     <row r="49">
@@ -2556,19 +2556,19 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.084216</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.03459</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.130632</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.148982</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.192043</v>
       </c>
     </row>
     <row r="71">
@@ -2584,19 +2584,19 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.084216</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.03459</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.130632</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.148982</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.192043</v>
       </c>
     </row>
     <row r="72">
@@ -2696,19 +2696,19 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.138798</v>
+        <v>0.054582</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.096734</v>
+        <v>0.062144</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.329081</v>
+        <v>1.198449</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.871362</v>
+        <v>1.72238</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.236623</v>
+        <v>2.04458</v>
       </c>
     </row>
     <row r="76">
@@ -2784,19 +2784,19 @@
         <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>1.225273</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>0.964787</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>1.057302</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>1.094901</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>0.978801</v>
       </c>
     </row>
     <row r="79">
@@ -2812,19 +2812,19 @@
         <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>1.225273</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>0.964787</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>1.057302</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0</v>
+        <v>1.094901</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0</v>
+        <v>0.978801</v>
       </c>
     </row>
     <row r="80">
@@ -2843,30 +2843,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>-0.2959889822007299</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-14.72465412326325</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>-0.7318433620337012</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>-0.9123818339719629</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.649794907171284</v>
       </c>
     </row>
     <row r="81">
@@ -2994,19 +2984,19 @@
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>5.19438</v>
+        <v>3.969107</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.022343</v>
+        <v>1.057556</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1.343981</v>
+        <v>0.286679</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2.769001</v>
+        <v>1.6741</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>3.180662</v>
+        <v>2.201861</v>
       </c>
     </row>
     <row r="86">
@@ -5186,7 +5176,11 @@
           <t>Current portion of lease obligations (Note 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -5427,7 +5421,11 @@
           <t>Lease obligations (Note 10)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -6292,7 +6290,11 @@
           <t>Current portion of lease obligations (Note 11)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -6439,7 +6441,11 @@
           <t>Lease obligations (Note 11)</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -7565,7 +7571,11 @@
           <t>Current portion of lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -7714,7 +7724,11 @@
           <t>Lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -10030,7 +10044,11 @@
           <t>Proceeds from issuance of units from private placement (Note 12)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -11240,7 +11258,11 @@
           <t>Proceeds from issuance of units from private placement (Note 13)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -14600,7 +14622,11 @@
           <t>Proceeds from issuance of units from private placement (Note 15)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -15559,7 +15585,11 @@
           <t>Proceeds from issuance of units from private placement (Note 15)</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
